--- a/tools/rating-extractor/exports/rating_records.xlsx
+++ b/tools/rating-extractor/exports/rating_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V793"/>
+  <dimension ref="A1:V809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53954,33 +53954,25 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>13,807.05 NCD programme (public placement) 195.56</t>
+          <t>Commercial Paper</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F671" t="n">
-        <v>13807.05</v>
+          <t>2023-02-28</t>
+        </is>
       </c>
       <c r="H671" t="n">
         <v>0</v>
       </c>
-      <c r="L671" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="M671" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="N671" t="n">
@@ -53991,35 +53983,32 @@
       </c>
       <c r="P671" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed SEBI (Positive); reaffirmed and'</t>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
         </is>
       </c>
       <c r="Q671" t="inlineStr">
         <is>
-          <t>summary_of_rating_action</t>
-        </is>
-      </c>
-      <c r="R671" t="n">
-        <v>2</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S671" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="T671" t="inlineStr">
         <is>
-          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/CholamandalamInvestmentandFinanceCompanyLimited_February%2024_%202026_RR_388994.html</t>
         </is>
       </c>
       <c r="U671" t="inlineStr">
         <is>
-          <t>13,807.05 NCD programme (public placement) 195.56 | prev 13,807.05 | curr - | (Positive); reaffirmed SEBI (Positive); reaffirmed and</t>
+          <t>28-02-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V671" t="inlineStr">
         <is>
-          <t>2026-09-09T16:54:44.652901+00:00</t>
+          <t>2026-09-10T15:56:14.352846+00:00</t>
         </is>
       </c>
     </row>
@@ -54031,59 +54020,66 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>13,807.05 NCD programme (public placement) 195.56</t>
+          <t>Commercial Paper</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="H672" t="n">
         <v>0</v>
       </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O672" t="n">
-        <v>1</v>
-      </c>
-      <c r="P672" t="inlineStr">
-        <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'SEBI'</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q672" t="inlineStr">
         <is>
-          <t>summary_of_rating_action</t>
-        </is>
-      </c>
-      <c r="R672" t="n">
-        <v>3</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S672" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="T672" t="inlineStr">
         <is>
-          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/CholamandalamInvestmentandFinanceCompanyLimited_February%2024_%202026_RR_388994.html</t>
         </is>
       </c>
       <c r="U672" t="inlineStr">
         <is>
-          <t>13,807.05 NCD programme (public placement) 195.56 | prev - | curr - | SEBI</t>
+          <t>28-02-24 Crisil A1+</t>
         </is>
       </c>
       <c r="V672" t="inlineStr">
         <is>
-          <t>2026-09-09T16:54:44.652901+00:00</t>
+          <t>2026-09-10T15:56:14.352846+00:00</t>
         </is>
       </c>
     </row>
@@ -54095,33 +54091,30 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00</t>
+          <t>Commercial Paper</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F673" t="n">
-        <v>32180.9</v>
-      </c>
-      <c r="G673" t="inlineStr">
-        <is>
-          <t>[ICRA]AA+</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H673" t="n">
         <v>0</v>
       </c>
-      <c r="L673" t="inlineStr">
-        <is>
-          <t>Positive</t>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
@@ -54130,42 +54123,34 @@
         </is>
       </c>
       <c r="N673" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O673" t="n">
-        <v>1</v>
-      </c>
-      <c r="P673" t="inlineStr">
-        <is>
-          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed SEBI (Positive); reaffirmed and'</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q673" t="inlineStr">
         <is>
-          <t>summary_of_rating_action</t>
-        </is>
-      </c>
-      <c r="R673" t="n">
-        <v>0</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S673" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="T673" t="inlineStr">
         <is>
-          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/CholamandalamInvestmentandFinanceCompanyLimited_February%2024_%202026_RR_388994.html</t>
         </is>
       </c>
       <c r="U673" t="inlineStr">
         <is>
-          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00 | prev 32,180.90 | curr [ICRA]AA+ | (Positive); reaffirmed SEBI (Positive); reaffirmed and</t>
+          <t>27-02-25 Crisil A1+</t>
         </is>
       </c>
       <c r="V673" t="inlineStr">
         <is>
-          <t>2026-09-09T16:54:44.652901+00:00</t>
+          <t>2026-09-10T15:56:14.352846+00:00</t>
         </is>
       </c>
     </row>
@@ -54177,59 +54162,66 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00</t>
+          <t>Commercial Paper</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H674" t="n">
         <v>0</v>
       </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N674" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O674" t="n">
-        <v>1</v>
-      </c>
-      <c r="P674" t="inlineStr">
-        <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'SEBI'</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q674" t="inlineStr">
         <is>
-          <t>summary_of_rating_action</t>
-        </is>
-      </c>
-      <c r="R674" t="n">
-        <v>1</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S674" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="T674" t="inlineStr">
         <is>
-          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/CholamandalamInvestmentandFinanceCompanyLimited_February%2024_%202026_RR_388994.html</t>
         </is>
       </c>
       <c r="U674" t="inlineStr">
         <is>
-          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00 | prev - | curr - | SEBI</t>
+          <t>30-12-25 Crisil A1+</t>
         </is>
       </c>
       <c r="V674" t="inlineStr">
         <is>
-          <t>2026-09-09T16:54:44.652901+00:00</t>
+          <t>2026-09-10T15:56:14.352846+00:00</t>
         </is>
       </c>
     </row>
@@ -54241,67 +54233,72 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Commercial paper 25,000.00</t>
+          <t>Commercial Paper</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F675" t="n">
-        <v>25000</v>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>12000</v>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>[ICRA]A1+;</t>
+          <t>Rs.12000Crore</t>
         </is>
       </c>
       <c r="H675" t="n">
         <v>0</v>
       </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O675" t="n">
-        <v>1</v>
-      </c>
-      <c r="P675" t="inlineStr">
-        <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'reaffirmed RBI'</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q675" t="inlineStr">
         <is>
-          <t>summary_of_rating_action</t>
+          <t>header_action_table</t>
         </is>
       </c>
       <c r="R675" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S675" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="T675" t="inlineStr">
         <is>
-          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/CholamandalamInvestmentandFinanceCompanyLimited_February%2024_%202026_RR_388994.html</t>
         </is>
       </c>
       <c r="U675" t="inlineStr">
         <is>
-          <t>Commercial paper 25,000.00 | prev 25,000.00 | curr [ICRA]A1+; | reaffirmed RBI</t>
+          <t>Rs.12000 Crore Commercial Paper | Crisil A1+ (Reaffirmed)</t>
         </is>
       </c>
       <c r="V675" t="inlineStr">
         <is>
-          <t>2026-09-09T16:54:44.652901+00:00</t>
+          <t>2026-09-10T15:56:14.352846+00:00</t>
         </is>
       </c>
     </row>
@@ -54318,7 +54315,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Fund-based facilities from 4,000.00</t>
+          <t>13,807.05 NCD programme (public placement) 195.56</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -54327,11 +54324,21 @@
         </is>
       </c>
       <c r="F676" t="n">
-        <v>4000</v>
+        <v>13807.05</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
       </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N676" t="n">
         <v>0</v>
       </c>
@@ -54340,7 +54347,7 @@
       </c>
       <c r="P676" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'RBI'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed SEBI (Positive); reaffirmed and'</t>
         </is>
       </c>
       <c r="Q676" t="inlineStr">
@@ -54349,7 +54356,7 @@
         </is>
       </c>
       <c r="R676" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S676" t="inlineStr">
         <is>
@@ -54363,7 +54370,7 @@
       </c>
       <c r="U676" t="inlineStr">
         <is>
-          <t>Fund-based facilities from 4,000.00 | prev 4,000.00 | curr - | RBI</t>
+          <t>13,807.05 NCD programme (public placement) 195.56 | prev 13,807.05 | curr - | (Positive); reaffirmed SEBI (Positive); reaffirmed and</t>
         </is>
       </c>
       <c r="V676" t="inlineStr">
@@ -54385,7 +54392,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Long term/Short term – Fund- 1,21,000.04 based/Non-fund based others</t>
+          <t>13,807.05 NCD programme (public placement) 195.56</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -54393,14 +54400,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F677" t="n">
-        <v>171000.04</v>
-      </c>
-      <c r="G677" t="inlineStr">
-        <is>
-          <t>reaffirmed/assigned</t>
-        </is>
-      </c>
       <c r="H677" t="n">
         <v>0</v>
       </c>
@@ -54412,7 +54411,7 @@
       </c>
       <c r="P677" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'for enhanced RBI'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: 'SEBI'</t>
         </is>
       </c>
       <c r="Q677" t="inlineStr">
@@ -54421,7 +54420,7 @@
         </is>
       </c>
       <c r="R677" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S677" t="inlineStr">
         <is>
@@ -54435,7 +54434,7 @@
       </c>
       <c r="U677" t="inlineStr">
         <is>
-          <t>Long term/Short term – Fund- 1,21,000.04 based/Non-fund based others | prev 1,71,000.04 | curr reaffirmed/assigned | for enhanced RBI</t>
+          <t>13,807.05 NCD programme (public placement) 195.56 | prev - | curr - | SEBI</t>
         </is>
       </c>
       <c r="V677" t="inlineStr">
@@ -54457,7 +54456,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Market-linked debentures 200.00</t>
+          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -54466,11 +54465,26 @@
         </is>
       </c>
       <c r="F678" t="n">
-        <v>200</v>
+        <v>32180.9</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>[ICRA]AA+</t>
+        </is>
       </c>
       <c r="H678" t="n">
         <v>0</v>
       </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N678" t="n">
         <v>0</v>
       </c>
@@ -54479,7 +54493,7 @@
       </c>
       <c r="P678" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'SEBI'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed SEBI (Positive); reaffirmed and'</t>
         </is>
       </c>
       <c r="Q678" t="inlineStr">
@@ -54488,7 +54502,7 @@
         </is>
       </c>
       <c r="R678" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S678" t="inlineStr">
         <is>
@@ -54502,7 +54516,7 @@
       </c>
       <c r="U678" t="inlineStr">
         <is>
-          <t>Market-linked debentures 200.00 | prev 200.00 | curr - | SEBI</t>
+          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00 | prev 32,180.90 | curr [ICRA]AA+ | (Positive); reaffirmed SEBI (Positive); reaffirmed and</t>
         </is>
       </c>
       <c r="V678" t="inlineStr">
@@ -54524,7 +54538,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>PDI 514.00</t>
+          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -54532,14 +54546,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F679" t="n">
-        <v>514</v>
-      </c>
-      <c r="G679" t="inlineStr">
-        <is>
-          <t>[ICRA]AA (Positive);</t>
-        </is>
-      </c>
       <c r="H679" t="n">
         <v>0</v>
       </c>
@@ -54551,7 +54557,7 @@
       </c>
       <c r="P679" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'reaffirmed MCA'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: 'SEBI'</t>
         </is>
       </c>
       <c r="Q679" t="inlineStr">
@@ -54560,7 +54566,7 @@
         </is>
       </c>
       <c r="R679" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S679" t="inlineStr">
         <is>
@@ -54574,7 +54580,7 @@
       </c>
       <c r="U679" t="inlineStr">
         <is>
-          <t>PDI 514.00 | prev 514.00 | curr [ICRA]AA (Positive); | reaffirmed MCA</t>
+          <t>32,180.90 Non-convertible debenture (NCD) programme 2,002.00 | prev - | curr - | SEBI</t>
         </is>
       </c>
       <c r="V679" t="inlineStr">
@@ -54596,7 +54602,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Perpetual debt instrument (PDI) 6,462.30</t>
+          <t>Commercial paper 25,000.00</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -54605,11 +54611,11 @@
         </is>
       </c>
       <c r="F680" t="n">
-        <v>6462.3</v>
+        <v>25000</v>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>[ICRA]AA (Positive);</t>
+          <t>[ICRA]A1+;</t>
         </is>
       </c>
       <c r="H680" t="n">
@@ -54623,7 +54629,7 @@
       </c>
       <c r="P680" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: 'reaffirmed SEBI'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: 'reaffirmed RBI'</t>
         </is>
       </c>
       <c r="Q680" t="inlineStr">
@@ -54632,7 +54638,7 @@
         </is>
       </c>
       <c r="R680" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S680" t="inlineStr">
         <is>
@@ -54646,7 +54652,7 @@
       </c>
       <c r="U680" t="inlineStr">
         <is>
-          <t>Perpetual debt instrument (PDI) 6,462.30 | prev 6,462.30 | curr [ICRA]AA (Positive); | reaffirmed SEBI</t>
+          <t>Commercial paper 25,000.00 | prev 25,000.00 | curr [ICRA]A1+; | reaffirmed RBI</t>
         </is>
       </c>
       <c r="V680" t="inlineStr">
@@ -54668,7 +54674,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Sub-limit – Non-fund based (100.00)</t>
+          <t>Fund-based facilities from 4,000.00</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -54677,26 +54683,11 @@
         </is>
       </c>
       <c r="F681" t="n">
-        <v>100</v>
-      </c>
-      <c r="G681" t="inlineStr">
-        <is>
-          <t>[ICRA]AA+</t>
-        </is>
+        <v>4000</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
       </c>
-      <c r="L681" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="M681" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N681" t="n">
         <v>0</v>
       </c>
@@ -54705,7 +54696,7 @@
       </c>
       <c r="P681" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed RBI'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: 'RBI'</t>
         </is>
       </c>
       <c r="Q681" t="inlineStr">
@@ -54714,7 +54705,7 @@
         </is>
       </c>
       <c r="R681" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S681" t="inlineStr">
         <is>
@@ -54728,7 +54719,7 @@
       </c>
       <c r="U681" t="inlineStr">
         <is>
-          <t>Sub-limit – Non-fund based (100.00) | prev (100.00) | curr [ICRA]AA+ | (Positive); reaffirmed RBI</t>
+          <t>Fund-based facilities from 4,000.00 | prev 4,000.00 | curr - | RBI</t>
         </is>
       </c>
       <c r="V681" t="inlineStr">
@@ -54750,7 +54741,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Subordinated debentures 18,310.00</t>
+          <t>Long term/Short term – Fund- 1,21,000.04 based/Non-fund based others</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -54759,26 +54750,16 @@
         </is>
       </c>
       <c r="F682" t="n">
-        <v>18310</v>
+        <v>171000.04</v>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>[ICRA]AA+</t>
+          <t>reaffirmed/assigned</t>
         </is>
       </c>
       <c r="H682" t="n">
         <v>0</v>
       </c>
-      <c r="L682" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="M682" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N682" t="n">
         <v>0</v>
       </c>
@@ -54787,7 +54768,7 @@
       </c>
       <c r="P682" t="inlineStr">
         <is>
-          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed SEBI'</t>
+          <t>Could not read an explicit rating and action from the summary table cell: 'for enhanced RBI'</t>
         </is>
       </c>
       <c r="Q682" t="inlineStr">
@@ -54796,7 +54777,7 @@
         </is>
       </c>
       <c r="R682" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S682" t="inlineStr">
         <is>
@@ -54810,7 +54791,7 @@
       </c>
       <c r="U682" t="inlineStr">
         <is>
-          <t>Subordinated debentures 18,310.00 | prev 18,310.00 | curr [ICRA]AA+ | (Positive); reaffirmed SEBI</t>
+          <t>Long term/Short term – Fund- 1,21,000.04 based/Non-fund based others | prev 1,71,000.04 | curr reaffirmed/assigned | for enhanced RBI</t>
         </is>
       </c>
       <c r="V682" t="inlineStr">
@@ -54822,37 +54803,30 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Cholamandalam Investment And Finance Company Limited</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Market-linked debentures 200.00</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>200</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
       </c>
-      <c r="J683" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L683" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
       <c r="N683" t="n">
         <v>0</v>
       </c>
@@ -54861,224 +54835,217 @@
       </c>
       <c r="P683" t="inlineStr">
         <is>
-          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
+          <t>Could not read an explicit rating and action from the summary table cell: 'SEBI'</t>
         </is>
       </c>
       <c r="Q683" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>summary_of_rating_action</t>
+        </is>
+      </c>
+      <c r="R683" t="n">
+        <v>7</v>
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="T683" t="inlineStr">
         <is>
-          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
+          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
         </is>
       </c>
       <c r="U683" t="inlineStr">
         <is>
-          <t>13-02-23 Crisil AAA/Stable</t>
+          <t>Market-linked debentures 200.00 | prev 200.00 | curr - | SEBI</t>
         </is>
       </c>
       <c r="V683" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-09T16:54:44.652901+00:00</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Cholamandalam Investment And Finance Company Limited</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>PDI 514.00</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>514</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>[ICRA]AA (Positive);</t>
         </is>
       </c>
       <c r="H684" t="n">
         <v>0</v>
       </c>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="J684" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L684" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="M684" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N684" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O684" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Could not read an explicit rating and action from the summary table cell: 'reaffirmed MCA'</t>
+        </is>
       </c>
       <c r="Q684" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>summary_of_rating_action</t>
+        </is>
+      </c>
+      <c r="R684" t="n">
+        <v>6</v>
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="T684" t="inlineStr">
         <is>
-          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
+          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
         </is>
       </c>
       <c r="U684" t="inlineStr">
         <is>
-          <t>30-03-23 Crisil AAA/Stable</t>
+          <t>PDI 514.00 | prev 514.00 | curr [ICRA]AA (Positive); | reaffirmed MCA</t>
         </is>
       </c>
       <c r="V684" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-09T16:54:44.652901+00:00</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Cholamandalam Investment And Finance Company Limited</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Perpetual debt instrument (PDI) 6,462.30</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>6462.3</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>[ICRA]AA (Positive);</t>
         </is>
       </c>
       <c r="H685" t="n">
         <v>0</v>
       </c>
-      <c r="I685" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="J685" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L685" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="M685" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N685" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O685" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>Could not read an explicit rating and action from the summary table cell: 'reaffirmed SEBI'</t>
+        </is>
       </c>
       <c r="Q685" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>summary_of_rating_action</t>
+        </is>
+      </c>
+      <c r="R685" t="n">
+        <v>5</v>
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="T685" t="inlineStr">
         <is>
-          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
+          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
         </is>
       </c>
       <c r="U685" t="inlineStr">
         <is>
-          <t>12-04-23 Crisil AAA/Stable</t>
+          <t>Perpetual debt instrument (PDI) 6,462.30 | prev 6,462.30 | curr [ICRA]AA (Positive); | reaffirmed SEBI</t>
         </is>
       </c>
       <c r="V685" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-09T16:54:44.652901+00:00</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Cholamandalam Investment And Finance Company Limited</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Sub-limit – Non-fund based (100.00)</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>100</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>[ICRA]AA+</t>
         </is>
       </c>
       <c r="H686" t="n">
         <v>0</v>
       </c>
-      <c r="I686" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="J686" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L686" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M686" t="inlineStr">
@@ -55087,74 +55054,80 @@
         </is>
       </c>
       <c r="N686" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O686" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed RBI'</t>
+        </is>
       </c>
       <c r="Q686" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>summary_of_rating_action</t>
+        </is>
+      </c>
+      <c r="R686" t="n">
+        <v>10</v>
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="T686" t="inlineStr">
         <is>
-          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
+          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
         </is>
       </c>
       <c r="U686" t="inlineStr">
         <is>
-          <t>01-08-23 Crisil AAA/Stable</t>
+          <t>Sub-limit – Non-fund based (100.00) | prev (100.00) | curr [ICRA]AA+ | (Positive); reaffirmed RBI</t>
         </is>
       </c>
       <c r="V686" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-09T16:54:44.652901+00:00</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Cholamandalam Investment And Finance Company Limited</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Subordinated debentures 18,310.00</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>18310</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>[ICRA]AA+</t>
         </is>
       </c>
       <c r="H687" t="n">
         <v>0</v>
       </c>
-      <c r="I687" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="J687" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M687" t="inlineStr">
@@ -55163,34 +55136,42 @@
         </is>
       </c>
       <c r="N687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O687" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Could not read an explicit rating and action from the summary table cell: '(Positive); reaffirmed SEBI'</t>
+        </is>
       </c>
       <c r="Q687" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>summary_of_rating_action</t>
+        </is>
+      </c>
+      <c r="R687" t="n">
+        <v>4</v>
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="T687" t="inlineStr">
         <is>
-          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
+          <t>https://www.icra.in/Rating/GetRationalReportFilePdf?id=145427</t>
         </is>
       </c>
       <c r="U687" t="inlineStr">
         <is>
-          <t>20-09-23 Crisil AAA/Stable</t>
+          <t>Subordinated debentures 18,310.00 | prev 18,310.00 | curr [ICRA]AA+ | (Positive); reaffirmed SEBI</t>
         </is>
       </c>
       <c r="V687" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-09T16:54:44.652901+00:00</t>
         </is>
       </c>
     </row>
@@ -55207,27 +55188,30 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Bank Loan Facilities (Long Term)</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Rs.10000.0 Crore</t>
         </is>
       </c>
       <c r="H688" t="n">
         <v>0</v>
       </c>
-      <c r="I688" t="inlineStr">
+      <c r="J688" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J688" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -55246,8 +55230,11 @@
       </c>
       <c r="Q688" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R688" t="n">
+        <v>0</v>
       </c>
       <c r="S688" t="inlineStr">
         <is>
@@ -55261,12 +55248,12 @@
       </c>
       <c r="U688" t="inlineStr">
         <is>
-          <t>25-10-23 Crisil AAA/Stable</t>
+          <t>Long Term Rating | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V688" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -55288,37 +55275,32 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H689" t="n">
         <v>0</v>
       </c>
-      <c r="I689" t="inlineStr">
+      <c r="J689" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J689" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="M689" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N689" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O689" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
+        </is>
       </c>
       <c r="Q689" t="inlineStr">
         <is>
@@ -55337,7 +55319,7 @@
       </c>
       <c r="U689" t="inlineStr">
         <is>
-          <t>25-01-24 Crisil AAA/Stable</t>
+          <t>13-02-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V689" t="inlineStr">
@@ -55364,7 +55346,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H690" t="n">
@@ -55413,7 +55395,7 @@
       </c>
       <c r="U690" t="inlineStr">
         <is>
-          <t>22-03-24 Crisil AAA/Stable</t>
+          <t>30-03-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V690" t="inlineStr">
@@ -55440,7 +55422,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H691" t="n">
@@ -55489,7 +55471,7 @@
       </c>
       <c r="U691" t="inlineStr">
         <is>
-          <t>21-03-25 Crisil AAA/Stable</t>
+          <t>12-04-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V691" t="inlineStr">
@@ -55516,7 +55498,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H692" t="n">
@@ -55565,7 +55547,7 @@
       </c>
       <c r="U692" t="inlineStr">
         <is>
-          <t>27-03-25 Crisil AAA/Stable</t>
+          <t>01-08-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V692" t="inlineStr">
@@ -55592,7 +55574,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="H693" t="n">
@@ -55641,7 +55623,7 @@
       </c>
       <c r="U693" t="inlineStr">
         <is>
-          <t>21-05-25 Crisil AAA/Stable</t>
+          <t>20-09-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V693" t="inlineStr">
@@ -55668,7 +55650,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H694" t="n">
@@ -55717,7 +55699,7 @@
       </c>
       <c r="U694" t="inlineStr">
         <is>
-          <t>29-07-25 Crisil AAA/Stable</t>
+          <t>25-10-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V694" t="inlineStr">
@@ -55744,7 +55726,7 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H695" t="n">
@@ -55793,7 +55775,7 @@
       </c>
       <c r="U695" t="inlineStr">
         <is>
-          <t>17-02-26 Crisil AAA/Stable</t>
+          <t>25-01-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V695" t="inlineStr">
@@ -55820,7 +55802,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H696" t="n">
@@ -55869,7 +55851,7 @@
       </c>
       <c r="U696" t="inlineStr">
         <is>
-          <t>26-03-26 Crisil AAA/Stable</t>
+          <t>22-03-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V696" t="inlineStr">
@@ -55896,7 +55878,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H697" t="n">
@@ -55945,7 +55927,7 @@
       </c>
       <c r="U697" t="inlineStr">
         <is>
-          <t>06-07-26 Crisil AAA/Stable</t>
+          <t>21-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V697" t="inlineStr">
@@ -55967,48 +55949,53 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="H698" t="n">
+        <v>0</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
+      <c r="N698" t="n">
+        <v>1</v>
+      </c>
+      <c r="O698" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>rating_history_annexure</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="H698" t="n">
-        <v>0</v>
-      </c>
-      <c r="J698" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L698" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N698" t="n">
-        <v>0</v>
-      </c>
-      <c r="O698" t="n">
-        <v>1</v>
-      </c>
-      <c r="P698" t="inlineStr">
-        <is>
-          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
-        </is>
-      </c>
-      <c r="Q698" t="inlineStr">
-        <is>
-          <t>rating_history_annexure</t>
-        </is>
-      </c>
-      <c r="S698" t="inlineStr">
-        <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
       <c r="T698" t="inlineStr">
         <is>
           <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
@@ -56016,7 +56003,7 @@
       </c>
       <c r="U698" t="inlineStr">
         <is>
-          <t>13-02-23 Crisil AAA/Stable</t>
+          <t>27-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V698" t="inlineStr">
@@ -56038,12 +56025,12 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H699" t="n">
@@ -56092,7 +56079,7 @@
       </c>
       <c r="U699" t="inlineStr">
         <is>
-          <t>30-03-23 Crisil AAA/Stable</t>
+          <t>21-05-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V699" t="inlineStr">
@@ -56114,12 +56101,12 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H700" t="n">
@@ -56168,7 +56155,7 @@
       </c>
       <c r="U700" t="inlineStr">
         <is>
-          <t>12-04-23 Crisil AAA/Stable</t>
+          <t>29-07-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V700" t="inlineStr">
@@ -56190,12 +56177,12 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H701" t="n">
@@ -56244,7 +56231,7 @@
       </c>
       <c r="U701" t="inlineStr">
         <is>
-          <t>01-08-23 Crisil AAA/Stable</t>
+          <t>17-02-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V701" t="inlineStr">
@@ -56266,12 +56253,12 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H702" t="n">
@@ -56320,7 +56307,7 @@
       </c>
       <c r="U702" t="inlineStr">
         <is>
-          <t>20-09-23 Crisil AAA/Stable</t>
+          <t>26-03-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V702" t="inlineStr">
@@ -56342,12 +56329,12 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H703" t="n">
@@ -56396,7 +56383,7 @@
       </c>
       <c r="U703" t="inlineStr">
         <is>
-          <t>25-10-23 Crisil AAA/Stable</t>
+          <t>06-07-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V703" t="inlineStr">
@@ -56418,27 +56405,30 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Fund Based Facilities</t>
+          <t>Bonds Aggregating #</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>16081.48</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Rs.16081.48Crore</t>
         </is>
       </c>
       <c r="H704" t="n">
         <v>0</v>
       </c>
-      <c r="I704" t="inlineStr">
+      <c r="J704" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J704" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -56457,8 +56447,11 @@
       </c>
       <c r="Q704" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R704" t="n">
+        <v>10</v>
       </c>
       <c r="S704" t="inlineStr">
         <is>
@@ -56472,12 +56465,12 @@
       </c>
       <c r="U704" t="inlineStr">
         <is>
-          <t>25-01-24 Crisil AAA/Stable</t>
+          <t>Bonds A ggregating Rs . 16 081.48 C rore# | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V704" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -56499,37 +56492,32 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H705" t="n">
         <v>0</v>
       </c>
-      <c r="I705" t="inlineStr">
+      <c r="J705" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J705" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="M705" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N705" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O705" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
+        </is>
       </c>
       <c r="Q705" t="inlineStr">
         <is>
@@ -56548,7 +56536,7 @@
       </c>
       <c r="U705" t="inlineStr">
         <is>
-          <t>22-03-24 Crisil AAA/Stable</t>
+          <t>13-02-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V705" t="inlineStr">
@@ -56575,7 +56563,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H706" t="n">
@@ -56624,7 +56612,7 @@
       </c>
       <c r="U706" t="inlineStr">
         <is>
-          <t>21-03-25 Crisil AAA/Stable</t>
+          <t>30-03-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V706" t="inlineStr">
@@ -56651,7 +56639,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H707" t="n">
@@ -56700,7 +56688,7 @@
       </c>
       <c r="U707" t="inlineStr">
         <is>
-          <t>27-03-25 Crisil AAA/Stable</t>
+          <t>12-04-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V707" t="inlineStr">
@@ -56727,7 +56715,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H708" t="n">
@@ -56776,7 +56764,7 @@
       </c>
       <c r="U708" t="inlineStr">
         <is>
-          <t>21-05-25 Crisil AAA/Stable</t>
+          <t>01-08-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V708" t="inlineStr">
@@ -56803,7 +56791,7 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="H709" t="n">
@@ -56852,7 +56840,7 @@
       </c>
       <c r="U709" t="inlineStr">
         <is>
-          <t>29-07-25 Crisil AAA/Stable</t>
+          <t>20-09-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V709" t="inlineStr">
@@ -56879,7 +56867,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H710" t="n">
@@ -56928,7 +56916,7 @@
       </c>
       <c r="U710" t="inlineStr">
         <is>
-          <t>17-02-26 Crisil AAA/Stable</t>
+          <t>25-10-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V710" t="inlineStr">
@@ -56955,7 +56943,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H711" t="n">
@@ -57004,7 +56992,7 @@
       </c>
       <c r="U711" t="inlineStr">
         <is>
-          <t>26-03-26 Crisil AAA/Stable</t>
+          <t>25-01-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V711" t="inlineStr">
@@ -57031,7 +57019,7 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H712" t="n">
@@ -57080,7 +57068,7 @@
       </c>
       <c r="U712" t="inlineStr">
         <is>
-          <t>06-07-26 Crisil AAA/Stable</t>
+          <t>22-03-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V712" t="inlineStr">
@@ -57102,48 +57090,53 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="H713" t="n">
+        <v>0</v>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
+      <c r="N713" t="n">
+        <v>1</v>
+      </c>
+      <c r="O713" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>rating_history_annexure</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="H713" t="n">
-        <v>0</v>
-      </c>
-      <c r="J713" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L713" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N713" t="n">
-        <v>0</v>
-      </c>
-      <c r="O713" t="n">
-        <v>1</v>
-      </c>
-      <c r="P713" t="inlineStr">
-        <is>
-          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
-        </is>
-      </c>
-      <c r="Q713" t="inlineStr">
-        <is>
-          <t>rating_history_annexure</t>
-        </is>
-      </c>
-      <c r="S713" t="inlineStr">
-        <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
       <c r="T713" t="inlineStr">
         <is>
           <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
@@ -57151,7 +57144,7 @@
       </c>
       <c r="U713" t="inlineStr">
         <is>
-          <t>13-02-23 Crisil AAA/Stable</t>
+          <t>21-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V713" t="inlineStr">
@@ -57173,12 +57166,12 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H714" t="n">
@@ -57227,7 +57220,7 @@
       </c>
       <c r="U714" t="inlineStr">
         <is>
-          <t>30-03-23 Crisil AAA/Stable</t>
+          <t>27-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V714" t="inlineStr">
@@ -57249,12 +57242,12 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H715" t="n">
@@ -57303,7 +57296,7 @@
       </c>
       <c r="U715" t="inlineStr">
         <is>
-          <t>12-04-23 Crisil AAA/Stable</t>
+          <t>21-05-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V715" t="inlineStr">
@@ -57325,12 +57318,12 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H716" t="n">
@@ -57379,7 +57372,7 @@
       </c>
       <c r="U716" t="inlineStr">
         <is>
-          <t>01-08-23 Crisil AAA/Stable</t>
+          <t>29-07-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V716" t="inlineStr">
@@ -57401,12 +57394,12 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H717" t="n">
@@ -57455,7 +57448,7 @@
       </c>
       <c r="U717" t="inlineStr">
         <is>
-          <t>20-09-23 Crisil AAA/Stable</t>
+          <t>17-02-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V717" t="inlineStr">
@@ -57477,12 +57470,12 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H718" t="n">
@@ -57531,7 +57524,7 @@
       </c>
       <c r="U718" t="inlineStr">
         <is>
-          <t>25-10-23 Crisil AAA/Stable</t>
+          <t>26-03-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V718" t="inlineStr">
@@ -57553,12 +57546,12 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Fund Based Facilities</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H719" t="n">
@@ -57607,7 +57600,7 @@
       </c>
       <c r="U719" t="inlineStr">
         <is>
-          <t>25-01-24 Crisil AAA/Stable</t>
+          <t>06-07-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V719" t="inlineStr">
@@ -57629,27 +57622,30 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Long Term Borrowing Programme Aggregating ~</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>390326.83</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Rs.390326.83Crore</t>
         </is>
       </c>
       <c r="H720" t="n">
         <v>0</v>
       </c>
-      <c r="I720" t="inlineStr">
+      <c r="J720" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J720" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -57668,8 +57664,11 @@
       </c>
       <c r="Q720" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R720" t="n">
+        <v>7</v>
       </c>
       <c r="S720" t="inlineStr">
         <is>
@@ -57683,12 +57682,12 @@
       </c>
       <c r="U720" t="inlineStr">
         <is>
-          <t>22-03-24 Crisil AAA/Stable</t>
+          <t>Long Term Borrowing Programme A ggregating Rs . 3 90 326.83 C rore (Reduced from Rs . 4 07 193.49 C rore)~ | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V720" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -57705,27 +57704,30 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Long Term Borrowing programme%</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>130000</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Rs.130000Crore</t>
         </is>
       </c>
       <c r="H721" t="n">
         <v>0</v>
       </c>
-      <c r="I721" t="inlineStr">
+      <c r="J721" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J721" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -57744,8 +57746,11 @@
       </c>
       <c r="Q721" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R721" t="n">
+        <v>2</v>
       </c>
       <c r="S721" t="inlineStr">
         <is>
@@ -57759,12 +57764,12 @@
       </c>
       <c r="U721" t="inlineStr">
         <is>
-          <t>21-03-25 Crisil AAA/Stable</t>
+          <t>Rs . 130 000 C rore Long Term Borrowing programme % | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V721" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -57781,27 +57786,30 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Long Term Borrowing programme% *</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Rs.10000Crore</t>
         </is>
       </c>
       <c r="H722" t="n">
         <v>0</v>
       </c>
-      <c r="I722" t="inlineStr">
+      <c r="J722" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -57820,8 +57828,11 @@
       </c>
       <c r="Q722" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R722" t="n">
+        <v>1</v>
       </c>
       <c r="S722" t="inlineStr">
         <is>
@@ -57835,12 +57846,12 @@
       </c>
       <c r="U722" t="inlineStr">
         <is>
-          <t>27-03-25 Crisil AAA/Stable</t>
+          <t>Rs . 10 000 C rore Long Term Borrowing programme % * | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V722" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -57857,27 +57868,30 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Long Term Borrowing programme^</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>115000</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Rs.115000Crore</t>
         </is>
       </c>
       <c r="H723" t="n">
         <v>0</v>
       </c>
-      <c r="I723" t="inlineStr">
+      <c r="J723" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J723" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -57896,8 +57910,11 @@
       </c>
       <c r="Q723" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R723" t="n">
+        <v>5</v>
       </c>
       <c r="S723" t="inlineStr">
         <is>
@@ -57911,12 +57928,12 @@
       </c>
       <c r="U723" t="inlineStr">
         <is>
-          <t>21-05-25 Crisil AAA/Stable</t>
+          <t>Rs . 115 000 C rore Long Term Borrowing programme^ | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V723" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -57933,27 +57950,30 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Long-Term Borrowing Programme</t>
+          <t>Long Term Borrowing programme^*</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Rs.10000Crore</t>
         </is>
       </c>
       <c r="H724" t="n">
         <v>0</v>
       </c>
-      <c r="I724" t="inlineStr">
+      <c r="J724" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J724" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>Stable</t>
@@ -57972,8 +57992,11 @@
       </c>
       <c r="Q724" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R724" t="n">
+        <v>4</v>
       </c>
       <c r="S724" t="inlineStr">
         <is>
@@ -57987,12 +58010,12 @@
       </c>
       <c r="U724" t="inlineStr">
         <is>
-          <t>29-07-25 Crisil AAA/Stable</t>
+          <t>Rs . 10 000 C rore Long Term Borrowing progra mme^* | Crisil AAA/Stable (Reaffirmed)</t>
         </is>
       </c>
       <c r="V724" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -58014,37 +58037,32 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H725" t="n">
         <v>0</v>
       </c>
-      <c r="I725" t="inlineStr">
+      <c r="J725" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J725" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="M725" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N725" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O725" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
+        </is>
       </c>
       <c r="Q725" t="inlineStr">
         <is>
@@ -58063,7 +58081,7 @@
       </c>
       <c r="U725" t="inlineStr">
         <is>
-          <t>17-02-26 Crisil AAA/Stable</t>
+          <t>13-02-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V725" t="inlineStr">
@@ -58090,7 +58108,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H726" t="n">
@@ -58139,7 +58157,7 @@
       </c>
       <c r="U726" t="inlineStr">
         <is>
-          <t>26-03-26 Crisil AAA/Stable</t>
+          <t>30-03-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V726" t="inlineStr">
@@ -58166,7 +58184,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H727" t="n">
@@ -58215,7 +58233,7 @@
       </c>
       <c r="U727" t="inlineStr">
         <is>
-          <t>06-07-26 Crisil AAA/Stable</t>
+          <t>12-04-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V727" t="inlineStr">
@@ -58237,48 +58255,53 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="H728" t="n">
+        <v>0</v>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
+      <c r="N728" t="n">
+        <v>1</v>
+      </c>
+      <c r="O728" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q728" t="inlineStr">
+        <is>
+          <t>rating_history_annexure</t>
+        </is>
+      </c>
+      <c r="S728" t="inlineStr">
+        <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="H728" t="n">
-        <v>0</v>
-      </c>
-      <c r="J728" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N728" t="n">
-        <v>0</v>
-      </c>
-      <c r="O728" t="n">
-        <v>1</v>
-      </c>
-      <c r="P728" t="inlineStr">
-        <is>
-          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
-        </is>
-      </c>
-      <c r="Q728" t="inlineStr">
-        <is>
-          <t>rating_history_annexure</t>
-        </is>
-      </c>
-      <c r="S728" t="inlineStr">
-        <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
       <c r="T728" t="inlineStr">
         <is>
           <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
@@ -58286,7 +58309,7 @@
       </c>
       <c r="U728" t="inlineStr">
         <is>
-          <t>13-02-23 Crisil AAA/Stable</t>
+          <t>01-08-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V728" t="inlineStr">
@@ -58308,12 +58331,12 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="H729" t="n">
@@ -58362,7 +58385,7 @@
       </c>
       <c r="U729" t="inlineStr">
         <is>
-          <t>30-03-23 Crisil AAA/Stable</t>
+          <t>20-09-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V729" t="inlineStr">
@@ -58384,12 +58407,12 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H730" t="n">
@@ -58438,7 +58461,7 @@
       </c>
       <c r="U730" t="inlineStr">
         <is>
-          <t>12-04-23 Crisil AAA/Stable</t>
+          <t>25-10-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V730" t="inlineStr">
@@ -58460,12 +58483,12 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H731" t="n">
@@ -58514,7 +58537,7 @@
       </c>
       <c r="U731" t="inlineStr">
         <is>
-          <t>01-08-23 Crisil AAA/Stable</t>
+          <t>25-01-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V731" t="inlineStr">
@@ -58536,12 +58559,12 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H732" t="n">
@@ -58590,7 +58613,7 @@
       </c>
       <c r="U732" t="inlineStr">
         <is>
-          <t>20-09-23 Crisil AAA/Stable</t>
+          <t>22-03-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V732" t="inlineStr">
@@ -58612,12 +58635,12 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H733" t="n">
@@ -58666,7 +58689,7 @@
       </c>
       <c r="U733" t="inlineStr">
         <is>
-          <t>25-10-23 Crisil AAA/Stable</t>
+          <t>21-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V733" t="inlineStr">
@@ -58688,12 +58711,12 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H734" t="n">
@@ -58742,7 +58765,7 @@
       </c>
       <c r="U734" t="inlineStr">
         <is>
-          <t>25-01-24 Crisil AAA/Stable</t>
+          <t>27-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V734" t="inlineStr">
@@ -58764,12 +58787,12 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H735" t="n">
@@ -58818,7 +58841,7 @@
       </c>
       <c r="U735" t="inlineStr">
         <is>
-          <t>22-03-24 Crisil AAA/Stable</t>
+          <t>21-05-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V735" t="inlineStr">
@@ -58840,12 +58863,12 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H736" t="n">
@@ -58894,7 +58917,7 @@
       </c>
       <c r="U736" t="inlineStr">
         <is>
-          <t>21-03-25 Crisil AAA/Stable</t>
+          <t>29-07-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V736" t="inlineStr">
@@ -58916,12 +58939,12 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H737" t="n">
@@ -58970,7 +58993,7 @@
       </c>
       <c r="U737" t="inlineStr">
         <is>
-          <t>27-03-25 Crisil AAA/Stable</t>
+          <t>17-02-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V737" t="inlineStr">
@@ -58992,12 +59015,12 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H738" t="n">
@@ -59046,7 +59069,7 @@
       </c>
       <c r="U738" t="inlineStr">
         <is>
-          <t>21-05-25 Crisil AAA/Stable</t>
+          <t>26-03-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V738" t="inlineStr">
@@ -59068,12 +59091,12 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Perpetual Non Convertible Debentures</t>
+          <t>Long-Term Borrowing Programme</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H739" t="n">
@@ -59122,7 +59145,7 @@
       </c>
       <c r="U739" t="inlineStr">
         <is>
-          <t>29-07-25 Crisil AAA/Stable</t>
+          <t>06-07-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V739" t="inlineStr">
@@ -59149,37 +59172,32 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H740" t="n">
         <v>0</v>
       </c>
-      <c r="I740" t="inlineStr">
+      <c r="J740" t="inlineStr">
         <is>
           <t>Crisil AAA</t>
         </is>
       </c>
-      <c r="J740" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="M740" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N740" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O740" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
+        </is>
       </c>
       <c r="Q740" t="inlineStr">
         <is>
@@ -59198,7 +59216,7 @@
       </c>
       <c r="U740" t="inlineStr">
         <is>
-          <t>17-02-26 Crisil AAA/Stable</t>
+          <t>13-02-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V740" t="inlineStr">
@@ -59220,43 +59238,53 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
+          <t>2023-03-30</t>
+        </is>
+      </c>
+      <c r="H741" t="n">
+        <v>0</v>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
+      <c r="N741" t="n">
+        <v>1</v>
+      </c>
+      <c r="O741" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q741" t="inlineStr">
+        <is>
+          <t>rating_history_annexure</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="H741" t="n">
-        <v>0</v>
-      </c>
-      <c r="J741" t="inlineStr">
-        <is>
-          <t>Crisil A1+</t>
-        </is>
-      </c>
-      <c r="N741" t="n">
-        <v>0</v>
-      </c>
-      <c r="O741" t="n">
-        <v>1</v>
-      </c>
-      <c r="P741" t="inlineStr">
-        <is>
-          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
-        </is>
-      </c>
-      <c r="Q741" t="inlineStr">
-        <is>
-          <t>rating_history_annexure</t>
-        </is>
-      </c>
-      <c r="S741" t="inlineStr">
-        <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
       <c r="T741" t="inlineStr">
         <is>
           <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
@@ -59264,7 +59292,7 @@
       </c>
       <c r="U741" t="inlineStr">
         <is>
-          <t>13-02-23 Crisil A1+</t>
+          <t>30-03-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V741" t="inlineStr">
@@ -59286,12 +59314,12 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H742" t="n">
@@ -59299,12 +59327,17 @@
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M742" t="inlineStr">
@@ -59335,7 +59368,7 @@
       </c>
       <c r="U742" t="inlineStr">
         <is>
-          <t>30-03-23 Crisil A1+</t>
+          <t>12-04-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V742" t="inlineStr">
@@ -59357,12 +59390,12 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H743" t="n">
@@ -59370,12 +59403,17 @@
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M743" t="inlineStr">
@@ -59406,7 +59444,7 @@
       </c>
       <c r="U743" t="inlineStr">
         <is>
-          <t>12-04-23 Crisil A1+</t>
+          <t>01-08-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V743" t="inlineStr">
@@ -59428,12 +59466,12 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="H744" t="n">
@@ -59441,12 +59479,17 @@
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M744" t="inlineStr">
@@ -59477,7 +59520,7 @@
       </c>
       <c r="U744" t="inlineStr">
         <is>
-          <t>01-08-23 Crisil A1+</t>
+          <t>20-09-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V744" t="inlineStr">
@@ -59499,12 +59542,12 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H745" t="n">
@@ -59512,12 +59555,17 @@
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M745" t="inlineStr">
@@ -59548,7 +59596,7 @@
       </c>
       <c r="U745" t="inlineStr">
         <is>
-          <t>20-09-23 Crisil A1+</t>
+          <t>25-10-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V745" t="inlineStr">
@@ -59570,12 +59618,12 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H746" t="n">
@@ -59583,12 +59631,17 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M746" t="inlineStr">
@@ -59619,7 +59672,7 @@
       </c>
       <c r="U746" t="inlineStr">
         <is>
-          <t>25-10-23 Crisil A1+</t>
+          <t>25-01-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V746" t="inlineStr">
@@ -59641,12 +59694,12 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H747" t="n">
@@ -59654,12 +59707,17 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M747" t="inlineStr">
@@ -59690,7 +59748,7 @@
       </c>
       <c r="U747" t="inlineStr">
         <is>
-          <t>25-01-24 Crisil A1+</t>
+          <t>22-03-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V747" t="inlineStr">
@@ -59712,12 +59770,12 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H748" t="n">
@@ -59725,12 +59783,17 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M748" t="inlineStr">
@@ -59761,7 +59824,7 @@
       </c>
       <c r="U748" t="inlineStr">
         <is>
-          <t>22-03-24 Crisil A1+</t>
+          <t>21-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V748" t="inlineStr">
@@ -59783,12 +59846,12 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H749" t="n">
@@ -59796,12 +59859,17 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M749" t="inlineStr">
@@ -59832,7 +59900,7 @@
       </c>
       <c r="U749" t="inlineStr">
         <is>
-          <t>21-03-25 Crisil A1+</t>
+          <t>27-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V749" t="inlineStr">
@@ -59854,12 +59922,12 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H750" t="n">
@@ -59867,12 +59935,17 @@
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M750" t="inlineStr">
@@ -59903,7 +59976,7 @@
       </c>
       <c r="U750" t="inlineStr">
         <is>
-          <t>27-03-25 Crisil A1+</t>
+          <t>21-05-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V750" t="inlineStr">
@@ -59925,12 +59998,12 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H751" t="n">
@@ -59938,12 +60011,17 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M751" t="inlineStr">
@@ -59974,7 +60052,7 @@
       </c>
       <c r="U751" t="inlineStr">
         <is>
-          <t>21-05-25 Crisil A1+</t>
+          <t>29-07-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V751" t="inlineStr">
@@ -59996,12 +60074,12 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Perpetual Non Convertible Debentures</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H752" t="n">
@@ -60009,12 +60087,17 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>Crisil A1+</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="M752" t="inlineStr">
@@ -60045,7 +60128,7 @@
       </c>
       <c r="U752" t="inlineStr">
         <is>
-          <t>29-07-25 Crisil A1+</t>
+          <t>17-02-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V752" t="inlineStr">
@@ -60067,27 +60150,30 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Short Term Borrowing programme</t>
+          <t>Short Term Borrowing Programme~</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>1347.25</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Rs.1347.25Crore</t>
         </is>
       </c>
       <c r="H753" t="n">
         <v>0</v>
       </c>
-      <c r="I753" t="inlineStr">
+      <c r="J753" t="inlineStr">
         <is>
           <t>Crisil A1+</t>
         </is>
       </c>
-      <c r="J753" t="inlineStr">
-        <is>
-          <t>Crisil A1+</t>
-        </is>
-      </c>
       <c r="M753" t="inlineStr">
         <is>
           <t>Reaffirmed</t>
@@ -60101,8 +60187,11 @@
       </c>
       <c r="Q753" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R753" t="n">
+        <v>8</v>
       </c>
       <c r="S753" t="inlineStr">
         <is>
@@ -60116,12 +60205,12 @@
       </c>
       <c r="U753" t="inlineStr">
         <is>
-          <t>17-02-26 Crisil A1+</t>
+          <t>Short Term Borrowing Programme Aggregating Rs . 1 347.25 C rore~ | Crisil A1+ (Reaffirmed)</t>
         </is>
       </c>
       <c r="V753" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -60143,32 +60232,27 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H754" t="n">
         <v>0</v>
       </c>
-      <c r="I754" t="inlineStr">
+      <c r="J754" t="inlineStr">
         <is>
           <t>Crisil A1+</t>
         </is>
       </c>
-      <c r="J754" t="inlineStr">
-        <is>
-          <t>Crisil A1+</t>
-        </is>
-      </c>
-      <c r="M754" t="inlineStr">
-        <is>
-          <t>Reaffirmed</t>
-        </is>
-      </c>
       <c r="N754" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O754" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
+        </is>
       </c>
       <c r="Q754" t="inlineStr">
         <is>
@@ -60187,7 +60271,7 @@
       </c>
       <c r="U754" t="inlineStr">
         <is>
-          <t>26-03-26 Crisil A1+</t>
+          <t>13-02-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V754" t="inlineStr">
@@ -60214,7 +60298,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H755" t="n">
@@ -60258,7 +60342,7 @@
       </c>
       <c r="U755" t="inlineStr">
         <is>
-          <t>06-07-26 Crisil A1+</t>
+          <t>30-03-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V755" t="inlineStr">
@@ -60280,48 +60364,48 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="H756" t="n">
+        <v>0</v>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>Crisil A1+</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
+      <c r="N756" t="n">
+        <v>1</v>
+      </c>
+      <c r="O756" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>rating_history_annexure</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="H756" t="n">
-        <v>0</v>
-      </c>
-      <c r="J756" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L756" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N756" t="n">
-        <v>0</v>
-      </c>
-      <c r="O756" t="n">
-        <v>1</v>
-      </c>
-      <c r="P756" t="inlineStr">
-        <is>
-          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
-        </is>
-      </c>
-      <c r="Q756" t="inlineStr">
-        <is>
-          <t>rating_history_annexure</t>
-        </is>
-      </c>
-      <c r="S756" t="inlineStr">
-        <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
       <c r="T756" t="inlineStr">
         <is>
           <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
@@ -60329,7 +60413,7 @@
       </c>
       <c r="U756" t="inlineStr">
         <is>
-          <t>13-02-23 Crisil AAA/Stable</t>
+          <t>12-04-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V756" t="inlineStr">
@@ -60351,12 +60435,12 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H757" t="n">
@@ -60364,17 +60448,12 @@
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L757" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M757" t="inlineStr">
@@ -60405,7 +60484,7 @@
       </c>
       <c r="U757" t="inlineStr">
         <is>
-          <t>30-03-23 Crisil AAA/Stable</t>
+          <t>01-08-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V757" t="inlineStr">
@@ -60427,12 +60506,12 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="H758" t="n">
@@ -60440,17 +60519,12 @@
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L758" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M758" t="inlineStr">
@@ -60481,7 +60555,7 @@
       </c>
       <c r="U758" t="inlineStr">
         <is>
-          <t>12-04-23 Crisil AAA/Stable</t>
+          <t>20-09-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V758" t="inlineStr">
@@ -60503,12 +60577,12 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H759" t="n">
@@ -60516,17 +60590,12 @@
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L759" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M759" t="inlineStr">
@@ -60557,7 +60626,7 @@
       </c>
       <c r="U759" t="inlineStr">
         <is>
-          <t>01-08-23 Crisil AAA/Stable</t>
+          <t>25-10-23 Crisil A1+</t>
         </is>
       </c>
       <c r="V759" t="inlineStr">
@@ -60579,12 +60648,12 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H760" t="n">
@@ -60592,17 +60661,12 @@
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L760" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M760" t="inlineStr">
@@ -60633,7 +60697,7 @@
       </c>
       <c r="U760" t="inlineStr">
         <is>
-          <t>20-09-23 Crisil AAA/Stable</t>
+          <t>25-01-24 Crisil A1+</t>
         </is>
       </c>
       <c r="V760" t="inlineStr">
@@ -60655,12 +60719,12 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H761" t="n">
@@ -60668,17 +60732,12 @@
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L761" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
@@ -60709,7 +60768,7 @@
       </c>
       <c r="U761" t="inlineStr">
         <is>
-          <t>25-10-23 Crisil AAA/Stable</t>
+          <t>22-03-24 Crisil A1+</t>
         </is>
       </c>
       <c r="V761" t="inlineStr">
@@ -60731,12 +60790,12 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H762" t="n">
@@ -60744,17 +60803,12 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L762" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M762" t="inlineStr">
@@ -60785,7 +60839,7 @@
       </c>
       <c r="U762" t="inlineStr">
         <is>
-          <t>25-01-24 Crisil AAA/Stable</t>
+          <t>21-03-25 Crisil A1+</t>
         </is>
       </c>
       <c r="V762" t="inlineStr">
@@ -60807,12 +60861,12 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H763" t="n">
@@ -60820,17 +60874,12 @@
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L763" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M763" t="inlineStr">
@@ -60861,7 +60910,7 @@
       </c>
       <c r="U763" t="inlineStr">
         <is>
-          <t>22-03-24 Crisil AAA/Stable</t>
+          <t>27-03-25 Crisil A1+</t>
         </is>
       </c>
       <c r="V763" t="inlineStr">
@@ -60883,12 +60932,12 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H764" t="n">
@@ -60896,17 +60945,12 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L764" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M764" t="inlineStr">
@@ -60937,7 +60981,7 @@
       </c>
       <c r="U764" t="inlineStr">
         <is>
-          <t>21-03-25 Crisil AAA/Stable</t>
+          <t>21-05-25 Crisil A1+</t>
         </is>
       </c>
       <c r="V764" t="inlineStr">
@@ -60959,12 +61003,12 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H765" t="n">
@@ -60972,17 +61016,12 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L765" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M765" t="inlineStr">
@@ -61013,7 +61052,7 @@
       </c>
       <c r="U765" t="inlineStr">
         <is>
-          <t>27-03-25 Crisil AAA/Stable</t>
+          <t>29-07-25 Crisil A1+</t>
         </is>
       </c>
       <c r="V765" t="inlineStr">
@@ -61035,12 +61074,12 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H766" t="n">
@@ -61048,17 +61087,12 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L766" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M766" t="inlineStr">
@@ -61089,7 +61123,7 @@
       </c>
       <c r="U766" t="inlineStr">
         <is>
-          <t>21-05-25 Crisil AAA/Stable</t>
+          <t>17-02-26 Crisil A1+</t>
         </is>
       </c>
       <c r="V766" t="inlineStr">
@@ -61111,12 +61145,12 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H767" t="n">
@@ -61124,17 +61158,12 @@
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L767" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M767" t="inlineStr">
@@ -61165,7 +61194,7 @@
       </c>
       <c r="U767" t="inlineStr">
         <is>
-          <t>29-07-25 Crisil AAA/Stable</t>
+          <t>26-03-26 Crisil A1+</t>
         </is>
       </c>
       <c r="V767" t="inlineStr">
@@ -61187,12 +61216,12 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H768" t="n">
@@ -61200,17 +61229,12 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L768" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M768" t="inlineStr">
@@ -61241,7 +61265,7 @@
       </c>
       <c r="U768" t="inlineStr">
         <is>
-          <t>17-02-26 Crisil AAA/Stable</t>
+          <t>06-07-26 Crisil A1+</t>
         </is>
       </c>
       <c r="V768" t="inlineStr">
@@ -61263,30 +61287,28 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme%</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>Rs.20000Crore</t>
         </is>
       </c>
       <c r="H769" t="n">
         <v>0</v>
       </c>
-      <c r="I769" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L769" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M769" t="inlineStr">
@@ -61302,8 +61324,11 @@
       </c>
       <c r="Q769" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R769" t="n">
+        <v>3</v>
       </c>
       <c r="S769" t="inlineStr">
         <is>
@@ -61317,12 +61342,12 @@
       </c>
       <c r="U769" t="inlineStr">
         <is>
-          <t>26-03-26 Crisil AAA/Stable</t>
+          <t>Rs . 20 000 C rore Short Term Borrowing programme % | Crisil A1+ (Reaffirmed)</t>
         </is>
       </c>
       <c r="V769" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -61339,30 +61364,28 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Subordinated Non-Convertible Debentures</t>
+          <t>Short Term Borrowing programme^</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Rs.15000Crore</t>
         </is>
       </c>
       <c r="H770" t="n">
         <v>0</v>
       </c>
-      <c r="I770" t="inlineStr">
-        <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>Crisil AAA</t>
-        </is>
-      </c>
-      <c r="L770" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil A1+</t>
         </is>
       </c>
       <c r="M770" t="inlineStr">
@@ -61378,8 +61401,11 @@
       </c>
       <c r="Q770" t="inlineStr">
         <is>
-          <t>rating_history_annexure</t>
-        </is>
+          <t>header_action_table</t>
+        </is>
+      </c>
+      <c r="R770" t="n">
+        <v>6</v>
       </c>
       <c r="S770" t="inlineStr">
         <is>
@@ -61393,12 +61419,12 @@
       </c>
       <c r="U770" t="inlineStr">
         <is>
-          <t>06-07-26 Crisil AAA/Stable</t>
+          <t>Rs . 15 000 C rore Short Term Borrowing programme^ | Crisil A1+ (Reaffirmed)</t>
         </is>
       </c>
       <c r="V770" t="inlineStr">
         <is>
-          <t>2026-09-09T17:07:11.184029+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -61410,25 +61436,25 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Bank Loan — Bank of Baroda</t>
+          <t>Subordinated Non Convertible Debentures Aggregating</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E771" t="n">
-        <v>1410.345</v>
+        <v>11000</v>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>INR 14103.45 million</t>
+          <t>Rs.11000Crore</t>
         </is>
       </c>
       <c r="H771" t="n">
@@ -61436,51 +61462,46 @@
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>IND A</t>
-        </is>
-      </c>
-      <c r="L771" t="inlineStr">
-        <is>
-          <t>Stable</t>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
         </is>
       </c>
       <c r="N771" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O771" t="n">
-        <v>1</v>
-      </c>
-      <c r="P771" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q771" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
+          <t>header_action_table</t>
         </is>
       </c>
       <c r="R771" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T771" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U771" t="inlineStr">
         <is>
-          <t>Bank Loan | Bank of Baroda | IND A(CE)/Stable | rated amount 14103.45 (INR million, as published)</t>
+          <t>Subordinated Non Convertible Debentures A ggregating Rs . 11 000 C rore | Crisil AAA/S table (Reaffirmed)</t>
         </is>
       </c>
       <c r="V771" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-10T15:57:00.772760+00:00</t>
         </is>
       </c>
     </row>
@@ -61492,25 +61513,17 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Bank Loan — Bank of Baroda</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="E772" t="n">
-        <v>1410.345</v>
-      </c>
-      <c r="G772" t="inlineStr">
-        <is>
-          <t>INR 14103.45 million</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H772" t="n">
@@ -61518,7 +61531,7 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L772" t="inlineStr">
@@ -61534,35 +61547,32 @@
       </c>
       <c r="P772" t="inlineStr">
         <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+          <t>Oldest entry in the displayed history window; no prior rating is shown, so the action that produced it is unknown.</t>
         </is>
       </c>
       <c r="Q772" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R772" t="n">
-        <v>0</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S772" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T772" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U772" t="inlineStr">
         <is>
-          <t>Bank Loan | Bank of Baroda | IND A(CE)/Stable | rated amount 14103.45 (INR million, as published)</t>
+          <t>13-02-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V772" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -61574,33 +61584,30 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Bank Loan — Bank of Baroda</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E773" t="n">
-        <v>936.606</v>
-      </c>
-      <c r="G773" t="inlineStr">
-        <is>
-          <t>INR 9366.06 million</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H773" t="n">
         <v>0</v>
       </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L773" t="inlineStr">
@@ -61610,7 +61617,7 @@
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>Affirmed</t>
+          <t>Reaffirmed</t>
         </is>
       </c>
       <c r="N773" t="n">
@@ -61621,30 +61628,27 @@
       </c>
       <c r="Q773" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R773" t="n">
-        <v>0</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S773" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T773" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U773" t="inlineStr">
         <is>
-          <t>Bank Loan | Bank of Baroda | IND A(CE)/Stable | rated amount 9366.06 (INR million, as published)</t>
+          <t>30-03-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V773" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -61656,33 +61660,30 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Bank Loan — Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="E774" t="n">
-        <v>2692.333</v>
-      </c>
-      <c r="G774" t="inlineStr">
-        <is>
-          <t>INR 26923.33 million</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H774" t="n">
         <v>0</v>
       </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L774" t="inlineStr">
@@ -61690,43 +61691,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N774" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O774" t="n">
-        <v>1</v>
-      </c>
-      <c r="P774" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q774" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R774" t="n">
-        <v>9</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S774" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T774" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U774" t="inlineStr">
         <is>
-          <t>Bank Loan | Bank of India | IND A(CE)/Stable | rated amount 26923.33 (INR million, as published)</t>
+          <t>12-04-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V774" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -61738,33 +61736,30 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Bank Loan — Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="E775" t="n">
-        <v>2692.333</v>
-      </c>
-      <c r="G775" t="inlineStr">
-        <is>
-          <t>INR 26923.33 million</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H775" t="n">
         <v>0</v>
       </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L775" t="inlineStr">
@@ -61772,43 +61767,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N775" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O775" t="n">
-        <v>1</v>
-      </c>
-      <c r="P775" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q775" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R775" t="n">
-        <v>1</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S775" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T775" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U775" t="inlineStr">
         <is>
-          <t>Bank Loan | Bank of India | IND A(CE)/Stable | rated amount 26923.33 (INR million, as published)</t>
+          <t>01-08-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V775" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -61820,33 +61812,30 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Bank Loan — Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E776" t="n">
-        <v>2045.263</v>
-      </c>
-      <c r="G776" t="inlineStr">
-        <is>
-          <t>INR 20452.63 million</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="H776" t="n">
         <v>0</v>
       </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L776" t="inlineStr">
@@ -61856,7 +61845,7 @@
       </c>
       <c r="M776" t="inlineStr">
         <is>
-          <t>Affirmed</t>
+          <t>Reaffirmed</t>
         </is>
       </c>
       <c r="N776" t="n">
@@ -61867,30 +61856,27 @@
       </c>
       <c r="Q776" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R776" t="n">
-        <v>1</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S776" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T776" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U776" t="inlineStr">
         <is>
-          <t>Bank Loan | Bank of India | IND A(CE)/Stable | rated amount 20452.63 (INR million, as published)</t>
+          <t>20-09-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V776" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -61902,33 +61888,30 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bank Loan — Canara Bank</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="E777" t="n">
-        <v>1915.173</v>
-      </c>
-      <c r="G777" t="inlineStr">
-        <is>
-          <t>INR 19151.73 million</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H777" t="n">
         <v>0</v>
       </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L777" t="inlineStr">
@@ -61936,43 +61919,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N777" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O777" t="n">
-        <v>1</v>
-      </c>
-      <c r="P777" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q777" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R777" t="n">
-        <v>10</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T777" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U777" t="inlineStr">
         <is>
-          <t>Bank Loan | Canara Bank | IND A(CE)/Stable | rated amount 19151.73 (INR million, as published)</t>
+          <t>25-10-23 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V777" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -61984,33 +61964,30 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Bank Loan — Canara Bank</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="E778" t="n">
-        <v>1915.173</v>
-      </c>
-      <c r="G778" t="inlineStr">
-        <is>
-          <t>INR 19151.73 million</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H778" t="n">
         <v>0</v>
       </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L778" t="inlineStr">
@@ -62018,43 +61995,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N778" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O778" t="n">
-        <v>1</v>
-      </c>
-      <c r="P778" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q778" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R778" t="n">
-        <v>2</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T778" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U778" t="inlineStr">
         <is>
-          <t>Bank Loan | Canara Bank | IND A(CE)/Stable | rated amount 19151.73 (INR million, as published)</t>
+          <t>25-01-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V778" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62066,33 +62040,30 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Bank Loan — Canara Bank</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E779" t="n">
-        <v>1452.42</v>
-      </c>
-      <c r="G779" t="inlineStr">
-        <is>
-          <t>INR 14524.2 million</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H779" t="n">
         <v>0</v>
       </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L779" t="inlineStr">
@@ -62102,7 +62073,7 @@
       </c>
       <c r="M779" t="inlineStr">
         <is>
-          <t>Affirmed</t>
+          <t>Reaffirmed</t>
         </is>
       </c>
       <c r="N779" t="n">
@@ -62113,30 +62084,27 @@
       </c>
       <c r="Q779" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R779" t="n">
-        <v>2</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S779" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T779" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U779" t="inlineStr">
         <is>
-          <t>Bank Loan | Canara Bank | IND A(CE)/Stable | rated amount 14524.2 (INR million, as published)</t>
+          <t>22-03-24 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V779" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62148,33 +62116,30 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Bank Loan — Indian Overseas Bank</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="E780" t="n">
-        <v>487.789</v>
-      </c>
-      <c r="G780" t="inlineStr">
-        <is>
-          <t>INR 4877.89 million</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H780" t="n">
         <v>0</v>
       </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L780" t="inlineStr">
@@ -62182,43 +62147,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N780" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O780" t="n">
-        <v>1</v>
-      </c>
-      <c r="P780" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q780" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R780" t="n">
-        <v>11</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S780" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T780" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U780" t="inlineStr">
         <is>
-          <t>Bank Loan | Indian Overseas Bank | IND A(CE)/Stable | rated amount 4877.89 (INR million, as published)</t>
+          <t>21-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V780" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62230,33 +62192,30 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Bank Loan — Indian Overseas Bank</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="E781" t="n">
-        <v>487.789</v>
-      </c>
-      <c r="G781" t="inlineStr">
-        <is>
-          <t>INR 4877.89 million</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H781" t="n">
         <v>0</v>
       </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L781" t="inlineStr">
@@ -62264,43 +62223,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N781" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O781" t="n">
-        <v>1</v>
-      </c>
-      <c r="P781" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q781" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R781" t="n">
-        <v>3</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S781" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T781" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U781" t="inlineStr">
         <is>
-          <t>Bank Loan | Indian Overseas Bank | IND A(CE)/Stable | rated amount 4877.89 (INR million, as published)</t>
+          <t>27-03-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V781" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62312,33 +62268,30 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Bank Loan — Indian Overseas Bank</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E782" t="n">
-        <v>1327.758</v>
-      </c>
-      <c r="G782" t="inlineStr">
-        <is>
-          <t>INR 13277.58 million</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H782" t="n">
         <v>0</v>
       </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
@@ -62348,7 +62301,7 @@
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>Affirmed</t>
+          <t>Reaffirmed</t>
         </is>
       </c>
       <c r="N782" t="n">
@@ -62359,30 +62312,27 @@
       </c>
       <c r="Q782" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R782" t="n">
-        <v>3</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S782" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T782" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U782" t="inlineStr">
         <is>
-          <t>Bank Loan | Indian Overseas Bank | IND A(CE)/Stable | rated amount 13277.58 (INR million, as published)</t>
+          <t>21-05-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V782" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62394,33 +62344,30 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Bank Loan — State Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="E783" t="n">
-        <v>1124.573</v>
-      </c>
-      <c r="G783" t="inlineStr">
-        <is>
-          <t>INR 11245.73 million</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H783" t="n">
         <v>0</v>
       </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L783" t="inlineStr">
@@ -62428,43 +62375,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N783" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O783" t="n">
-        <v>1</v>
-      </c>
-      <c r="P783" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q783" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R783" t="n">
-        <v>12</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S783" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T783" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U783" t="inlineStr">
         <is>
-          <t>Bank Loan | State Bank of India | IND A(CE)/Stable | rated amount 11245.73 (INR million, as published)</t>
+          <t>29-07-25 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V783" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62476,33 +62420,30 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Bank Loan — State Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="E784" t="n">
-        <v>1124.573</v>
-      </c>
-      <c r="G784" t="inlineStr">
-        <is>
-          <t>INR 11245.73 million</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="H784" t="n">
         <v>0</v>
       </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L784" t="inlineStr">
@@ -62510,43 +62451,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N784" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O784" t="n">
-        <v>1</v>
-      </c>
-      <c r="P784" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q784" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R784" t="n">
-        <v>4</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S784" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T784" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U784" t="inlineStr">
         <is>
-          <t>Bank Loan | State Bank of India | IND A(CE)/Stable | rated amount 11245.73 (INR million, as published)</t>
+          <t>17-02-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V784" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62558,33 +62496,30 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Bank Loan — State Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E785" t="n">
-        <v>3391.016000000001</v>
-      </c>
-      <c r="G785" t="inlineStr">
-        <is>
-          <t>INR 33910.16 million</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H785" t="n">
         <v>0</v>
       </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
@@ -62594,7 +62529,7 @@
       </c>
       <c r="M785" t="inlineStr">
         <is>
-          <t>Affirmed</t>
+          <t>Reaffirmed</t>
         </is>
       </c>
       <c r="N785" t="n">
@@ -62605,30 +62540,27 @@
       </c>
       <c r="Q785" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R785" t="n">
-        <v>4</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S785" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T785" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U785" t="inlineStr">
         <is>
-          <t>Bank Loan | State Bank of India | IND A(CE)/Stable | rated amount 33910.16 (INR million, as published)</t>
+          <t>26-03-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V785" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62640,33 +62572,30 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>India Ratings</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bank Loan — Union Bank of India</t>
+          <t>Subordinated Non-Convertible Debentures</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="E786" t="n">
-        <v>1386.382</v>
-      </c>
-      <c r="G786" t="inlineStr">
-        <is>
-          <t>INR 13863.82 million</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H786" t="n">
         <v>0</v>
       </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Crisil AAA</t>
+        </is>
+      </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>IND A</t>
+          <t>Crisil AAA</t>
         </is>
       </c>
       <c r="L786" t="inlineStr">
@@ -62674,43 +62603,40 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>Reaffirmed</t>
+        </is>
+      </c>
       <c r="N786" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O786" t="n">
-        <v>1</v>
-      </c>
-      <c r="P786" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q786" t="inlineStr">
         <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R786" t="n">
-        <v>14</v>
+          <t>rating_history_annexure</t>
+        </is>
       </c>
       <c r="S786" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="T786" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.crisilratings.com/mnt/winshare/Ratings/RatingList/RatingDocs/PowerFinanceCorporationLimited_August%2005_%202026_RR_401595.html</t>
         </is>
       </c>
       <c r="U786" t="inlineStr">
         <is>
-          <t>Bank Loan | Union Bank of India | IND A(CE)/Stable | rated amount 13863.82 (INR million, as published)</t>
+          <t>06-07-26 Crisil AAA/Stable</t>
         </is>
       </c>
       <c r="V786" t="inlineStr">
         <is>
-          <t>2026-09-09T16:45:21.491896+00:00</t>
+          <t>2026-09-09T17:07:11.184029+00:00</t>
         </is>
       </c>
     </row>
@@ -62727,59 +62653,59 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Bank Loan — Union Bank of India</t>
+          <t>Bank Loan — Bank of Baroda</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>1410.345</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>INR 14103.45 million</t>
+        </is>
+      </c>
+      <c r="H787" t="n">
+        <v>0</v>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N787" t="n">
+        <v>0</v>
+      </c>
+      <c r="O787" t="n">
+        <v>1</v>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q787" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R787" t="n">
+        <v>8</v>
+      </c>
+      <c r="S787" t="inlineStr">
+        <is>
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="E787" t="n">
-        <v>1386.382</v>
-      </c>
-      <c r="G787" t="inlineStr">
-        <is>
-          <t>INR 13863.82 million</t>
-        </is>
-      </c>
-      <c r="H787" t="n">
-        <v>0</v>
-      </c>
-      <c r="J787" t="inlineStr">
-        <is>
-          <t>IND A</t>
-        </is>
-      </c>
-      <c r="L787" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N787" t="n">
-        <v>0</v>
-      </c>
-      <c r="O787" t="n">
-        <v>1</v>
-      </c>
-      <c r="P787" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
-      </c>
-      <c r="Q787" t="inlineStr">
-        <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R787" t="n">
-        <v>6</v>
-      </c>
-      <c r="S787" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
       <c r="T787" t="inlineStr">
         <is>
           <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
@@ -62787,7 +62713,7 @@
       </c>
       <c r="U787" t="inlineStr">
         <is>
-          <t>Bank Loan | Union Bank of India | IND A(CE)/Stable | rated amount 13863.82 (INR million, as published)</t>
+          <t>Bank Loan | Bank of Baroda | IND A(CE)/Stable | rated amount 14103.45 (INR million, as published)</t>
         </is>
       </c>
       <c r="V787" t="inlineStr">
@@ -62809,20 +62735,20 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Bank Loan — Union Bank of India</t>
+          <t>Bank Loan — Bank of Baroda</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E788" t="n">
-        <v>3058.023</v>
+        <v>1410.345</v>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>INR 30580.23 million</t>
+          <t>INR 14103.45 million</t>
         </is>
       </c>
       <c r="H788" t="n">
@@ -62838,16 +62764,16 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="M788" t="inlineStr">
-        <is>
-          <t>Affirmed</t>
-        </is>
-      </c>
       <c r="N788" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O788" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
       </c>
       <c r="Q788" t="inlineStr">
         <is>
@@ -62855,21 +62781,21 @@
         </is>
       </c>
       <c r="R788" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S788" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="T788" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
         </is>
       </c>
       <c r="U788" t="inlineStr">
         <is>
-          <t>Bank Loan | Union Bank of India | IND A(CE)/Stable | rated amount 30580.23 (INR million, as published)</t>
+          <t>Bank Loan | Bank of Baroda | IND A(CE)/Stable | rated amount 14103.45 (INR million, as published)</t>
         </is>
       </c>
       <c r="V788" t="inlineStr">
@@ -62891,20 +62817,20 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Bank loan — State Bank of India</t>
+          <t>Bank Loan — Bank of Baroda</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E789" t="n">
-        <v>750</v>
+        <v>936.606</v>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>INR 7500 million</t>
+          <t>INR 9366.06 million</t>
         </is>
       </c>
       <c r="H789" t="n">
@@ -62920,16 +62846,16 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>Affirmed</t>
+        </is>
+      </c>
       <c r="N789" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O789" t="n">
-        <v>1</v>
-      </c>
-      <c r="P789" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q789" t="inlineStr">
         <is>
@@ -62937,21 +62863,21 @@
         </is>
       </c>
       <c r="R789" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S789" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="T789" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
         </is>
       </c>
       <c r="U789" t="inlineStr">
         <is>
-          <t>Bank loan | State Bank of India | IND A(CE)/Stable | rated amount 7500 (INR million, as published)</t>
+          <t>Bank Loan | Bank of Baroda | IND A(CE)/Stable | rated amount 9366.06 (INR million, as published)</t>
         </is>
       </c>
       <c r="V789" t="inlineStr">
@@ -62973,59 +62899,59 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Bank loan — State Bank of India</t>
+          <t>Bank Loan — Bank of India</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>2692.333</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>INR 26923.33 million</t>
+        </is>
+      </c>
+      <c r="H790" t="n">
+        <v>0</v>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N790" t="n">
+        <v>0</v>
+      </c>
+      <c r="O790" t="n">
+        <v>1</v>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q790" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R790" t="n">
+        <v>9</v>
+      </c>
+      <c r="S790" t="inlineStr">
+        <is>
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="E790" t="n">
-        <v>750</v>
-      </c>
-      <c r="G790" t="inlineStr">
-        <is>
-          <t>INR 7500 million</t>
-        </is>
-      </c>
-      <c r="H790" t="n">
-        <v>0</v>
-      </c>
-      <c r="J790" t="inlineStr">
-        <is>
-          <t>IND A</t>
-        </is>
-      </c>
-      <c r="L790" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N790" t="n">
-        <v>0</v>
-      </c>
-      <c r="O790" t="n">
-        <v>1</v>
-      </c>
-      <c r="P790" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
-      </c>
-      <c r="Q790" t="inlineStr">
-        <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R790" t="n">
-        <v>5</v>
-      </c>
-      <c r="S790" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
       <c r="T790" t="inlineStr">
         <is>
           <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
@@ -63033,7 +62959,7 @@
       </c>
       <c r="U790" t="inlineStr">
         <is>
-          <t>Bank loan | State Bank of India | IND A(CE)/Stable | rated amount 7500 (INR million, as published)</t>
+          <t>Bank Loan | Bank of India | IND A(CE)/Stable | rated amount 26923.33 (INR million, as published)</t>
         </is>
       </c>
       <c r="V790" t="inlineStr">
@@ -63055,20 +62981,20 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Proposed Bank Loan — NA</t>
+          <t>Bank Loan — Bank of India</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E791" t="n">
-        <v>6233.405000000001</v>
+        <v>2692.333</v>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>INR 62334.05 million</t>
+          <t>INR 26923.33 million</t>
         </is>
       </c>
       <c r="H791" t="n">
@@ -63101,7 +63027,7 @@
         </is>
       </c>
       <c r="R791" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="S791" t="inlineStr">
         <is>
@@ -63115,7 +63041,7 @@
       </c>
       <c r="U791" t="inlineStr">
         <is>
-          <t>Proposed Bank Loan | NA | Provisional IND A(CE)/Stable | rated amount 62334.05 (INR million, as published)</t>
+          <t>Bank Loan | Bank of India | IND A(CE)/Stable | rated amount 26923.33 (INR million, as published)</t>
         </is>
       </c>
       <c r="V791" t="inlineStr">
@@ -63137,20 +63063,20 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Proposed Bank Loan — NA</t>
+          <t>Bank Loan — Bank of India</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E792" t="n">
-        <v>6233.405000000001</v>
+        <v>2045.263</v>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>INR 62334.05 million</t>
+          <t>INR 20452.63 million</t>
         </is>
       </c>
       <c r="H792" t="n">
@@ -63166,16 +63092,16 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>Affirmed</t>
+        </is>
+      </c>
       <c r="N792" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O792" t="n">
-        <v>1</v>
-      </c>
-      <c r="P792" t="inlineStr">
-        <is>
-          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="Q792" t="inlineStr">
         <is>
@@ -63183,21 +63109,21 @@
         </is>
       </c>
       <c r="R792" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S792" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="T792" t="inlineStr">
         <is>
-          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
         </is>
       </c>
       <c r="U792" t="inlineStr">
         <is>
-          <t>Proposed Bank Loan | NA | Provisional IND A(CE)/Stable | rated amount 62334.05 (INR million, as published)</t>
+          <t>Bank Loan | Bank of India | IND A(CE)/Stable | rated amount 20452.63 (INR million, as published)</t>
         </is>
       </c>
       <c r="V792" t="inlineStr">
@@ -63219,70 +63145,1382 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
+          <t>Bank Loan — Canara Bank</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>1915.173</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>INR 19151.73 million</t>
+        </is>
+      </c>
+      <c r="H793" t="n">
+        <v>0</v>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N793" t="n">
+        <v>0</v>
+      </c>
+      <c r="O793" t="n">
+        <v>1</v>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q793" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R793" t="n">
+        <v>10</v>
+      </c>
+      <c r="S793" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T793" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U793" t="inlineStr">
+        <is>
+          <t>Bank Loan | Canara Bank | IND A(CE)/Stable | rated amount 19151.73 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V793" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Bank Loan — Canara Bank</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>1915.173</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>INR 19151.73 million</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>0</v>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N794" t="n">
+        <v>0</v>
+      </c>
+      <c r="O794" t="n">
+        <v>1</v>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q794" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R794" t="n">
+        <v>2</v>
+      </c>
+      <c r="S794" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T794" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U794" t="inlineStr">
+        <is>
+          <t>Bank Loan | Canara Bank | IND A(CE)/Stable | rated amount 19151.73 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V794" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Bank Loan — Canara Bank</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>1452.42</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>INR 14524.2 million</t>
+        </is>
+      </c>
+      <c r="H795" t="n">
+        <v>0</v>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>Affirmed</t>
+        </is>
+      </c>
+      <c r="N795" t="n">
+        <v>1</v>
+      </c>
+      <c r="O795" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q795" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R795" t="n">
+        <v>2</v>
+      </c>
+      <c r="S795" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="T795" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+        </is>
+      </c>
+      <c r="U795" t="inlineStr">
+        <is>
+          <t>Bank Loan | Canara Bank | IND A(CE)/Stable | rated amount 14524.2 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V795" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Bank Loan — Indian Overseas Bank</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>487.789</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>INR 4877.89 million</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>0</v>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N796" t="n">
+        <v>0</v>
+      </c>
+      <c r="O796" t="n">
+        <v>1</v>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q796" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R796" t="n">
+        <v>11</v>
+      </c>
+      <c r="S796" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T796" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U796" t="inlineStr">
+        <is>
+          <t>Bank Loan | Indian Overseas Bank | IND A(CE)/Stable | rated amount 4877.89 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V796" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Bank Loan — Indian Overseas Bank</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>487.789</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>INR 4877.89 million</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>0</v>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N797" t="n">
+        <v>0</v>
+      </c>
+      <c r="O797" t="n">
+        <v>1</v>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q797" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R797" t="n">
+        <v>3</v>
+      </c>
+      <c r="S797" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T797" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U797" t="inlineStr">
+        <is>
+          <t>Bank Loan | Indian Overseas Bank | IND A(CE)/Stable | rated amount 4877.89 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V797" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Bank Loan — Indian Overseas Bank</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>1327.758</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>INR 13277.58 million</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>0</v>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>Affirmed</t>
+        </is>
+      </c>
+      <c r="N798" t="n">
+        <v>1</v>
+      </c>
+      <c r="O798" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q798" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R798" t="n">
+        <v>3</v>
+      </c>
+      <c r="S798" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="T798" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+        </is>
+      </c>
+      <c r="U798" t="inlineStr">
+        <is>
+          <t>Bank Loan | Indian Overseas Bank | IND A(CE)/Stable | rated amount 13277.58 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V798" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Bank Loan — State Bank of India</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>1124.573</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>INR 11245.73 million</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>0</v>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N799" t="n">
+        <v>0</v>
+      </c>
+      <c r="O799" t="n">
+        <v>1</v>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q799" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R799" t="n">
+        <v>12</v>
+      </c>
+      <c r="S799" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T799" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U799" t="inlineStr">
+        <is>
+          <t>Bank Loan | State Bank of India | IND A(CE)/Stable | rated amount 11245.73 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V799" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Bank Loan — State Bank of India</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>1124.573</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>INR 11245.73 million</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>0</v>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N800" t="n">
+        <v>0</v>
+      </c>
+      <c r="O800" t="n">
+        <v>1</v>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q800" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R800" t="n">
+        <v>4</v>
+      </c>
+      <c r="S800" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T800" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U800" t="inlineStr">
+        <is>
+          <t>Bank Loan | State Bank of India | IND A(CE)/Stable | rated amount 11245.73 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V800" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Bank Loan — State Bank of India</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>3391.016000000001</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>INR 33910.16 million</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>0</v>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>Affirmed</t>
+        </is>
+      </c>
+      <c r="N801" t="n">
+        <v>1</v>
+      </c>
+      <c r="O801" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q801" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R801" t="n">
+        <v>4</v>
+      </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="T801" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+        </is>
+      </c>
+      <c r="U801" t="inlineStr">
+        <is>
+          <t>Bank Loan | State Bank of India | IND A(CE)/Stable | rated amount 33910.16 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V801" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Bank Loan — Union Bank of India</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>1386.382</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>INR 13863.82 million</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>0</v>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N802" t="n">
+        <v>0</v>
+      </c>
+      <c r="O802" t="n">
+        <v>1</v>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q802" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R802" t="n">
+        <v>14</v>
+      </c>
+      <c r="S802" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T802" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>Bank Loan | Union Bank of India | IND A(CE)/Stable | rated amount 13863.82 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V802" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Bank Loan — Union Bank of India</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>1386.382</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>INR 13863.82 million</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>0</v>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N803" t="n">
+        <v>0</v>
+      </c>
+      <c r="O803" t="n">
+        <v>1</v>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q803" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R803" t="n">
+        <v>6</v>
+      </c>
+      <c r="S803" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T803" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U803" t="inlineStr">
+        <is>
+          <t>Bank Loan | Union Bank of India | IND A(CE)/Stable | rated amount 13863.82 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V803" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Bank Loan — Union Bank of India</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>3058.023</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>INR 30580.23 million</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>0</v>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>Affirmed</t>
+        </is>
+      </c>
+      <c r="N804" t="n">
+        <v>1</v>
+      </c>
+      <c r="O804" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q804" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R804" t="n">
+        <v>5</v>
+      </c>
+      <c r="S804" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="T804" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
+        </is>
+      </c>
+      <c r="U804" t="inlineStr">
+        <is>
+          <t>Bank Loan | Union Bank of India | IND A(CE)/Stable | rated amount 30580.23 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V804" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Bank loan — State Bank of India</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>750</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>INR 7500 million</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>0</v>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N805" t="n">
+        <v>0</v>
+      </c>
+      <c r="O805" t="n">
+        <v>1</v>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q805" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R805" t="n">
+        <v>13</v>
+      </c>
+      <c r="S805" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T805" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U805" t="inlineStr">
+        <is>
+          <t>Bank loan | State Bank of India | IND A(CE)/Stable | rated amount 7500 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V805" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Bank loan — State Bank of India</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>750</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>INR 7500 million</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>0</v>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N806" t="n">
+        <v>0</v>
+      </c>
+      <c r="O806" t="n">
+        <v>1</v>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q806" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R806" t="n">
+        <v>5</v>
+      </c>
+      <c r="S806" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T806" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U806" t="inlineStr">
+        <is>
+          <t>Bank loan | State Bank of India | IND A(CE)/Stable | rated amount 7500 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V806" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
           <t>Proposed Bank Loan — NA</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr">
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>6233.405000000001</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>INR 62334.05 million</t>
+        </is>
+      </c>
+      <c r="H807" t="n">
+        <v>0</v>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N807" t="n">
+        <v>0</v>
+      </c>
+      <c r="O807" t="n">
+        <v>1</v>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q807" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R807" t="n">
+        <v>15</v>
+      </c>
+      <c r="S807" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T807" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U807" t="inlineStr">
+        <is>
+          <t>Proposed Bank Loan | NA | Provisional IND A(CE)/Stable | rated amount 62334.05 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V807" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Proposed Bank Loan — NA</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>6233.405000000001</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>INR 62334.05 million</t>
+        </is>
+      </c>
+      <c r="H808" t="n">
+        <v>0</v>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>IND A</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N808" t="n">
+        <v>0</v>
+      </c>
+      <c r="O808" t="n">
+        <v>1</v>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>The press release title states multiple actions (Assigned, Affirmed); which one applies to this instrument is not determinable from the facility endpoint, so it is not attributed.</t>
+        </is>
+      </c>
+      <c r="Q808" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R808" t="n">
+        <v>7</v>
+      </c>
+      <c r="S808" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="T808" t="inlineStr">
+        <is>
+          <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=76305</t>
+        </is>
+      </c>
+      <c r="U808" t="inlineStr">
+        <is>
+          <t>Proposed Bank Loan | NA | Provisional IND A(CE)/Stable | rated amount 62334.05 (INR million, as published)</t>
+        </is>
+      </c>
+      <c r="V808" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:45:21.491896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>India Ratings</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Proposed Bank Loan — NA</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="E793" t="n">
+      <c r="E809" t="n">
         <v>1233.405</v>
       </c>
-      <c r="G793" t="inlineStr">
+      <c r="G809" t="inlineStr">
         <is>
           <t>INR 12334.05 million</t>
         </is>
       </c>
-      <c r="H793" t="n">
-        <v>0</v>
-      </c>
-      <c r="J793" t="inlineStr">
+      <c r="H809" t="n">
+        <v>0</v>
+      </c>
+      <c r="J809" t="inlineStr">
         <is>
           <t>IND A</t>
         </is>
       </c>
-      <c r="L793" t="inlineStr">
+      <c r="L809" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="M793" t="inlineStr">
+      <c r="M809" t="inlineStr">
         <is>
           <t>Affirmed</t>
         </is>
       </c>
-      <c r="N793" t="n">
-        <v>1</v>
-      </c>
-      <c r="O793" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q793" t="inlineStr">
-        <is>
-          <t>bank_facility_rating_letter</t>
-        </is>
-      </c>
-      <c r="R793" t="n">
+      <c r="N809" t="n">
+        <v>1</v>
+      </c>
+      <c r="O809" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q809" t="inlineStr">
+        <is>
+          <t>bank_facility_rating_letter</t>
+        </is>
+      </c>
+      <c r="R809" t="n">
         <v>6</v>
       </c>
-      <c r="S793" t="inlineStr">
+      <c r="S809" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="T793" t="inlineStr">
+      <c r="T809" t="inlineStr">
         <is>
           <t>https://www.indiaratings.co.in/pressReleases/GetBankFacilityDataRatingLetter?pressReleaseId=84119</t>
         </is>
       </c>
-      <c r="U793" t="inlineStr">
+      <c r="U809" t="inlineStr">
         <is>
           <t>Proposed Bank Loan | NA | Provisional IND A(CE)/Stable | rated amount 12334.05 (INR million, as published)</t>
         </is>
       </c>
-      <c r="V793" t="inlineStr">
+      <c r="V809" t="inlineStr">
         <is>
           <t>2026-09-09T16:45:21.491896+00:00</t>
         </is>
